--- a/Development/Longitudinal/foo.xlsx
+++ b/Development/Longitudinal/foo.xlsx
@@ -10,26 +10,6 @@
   </sheets>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>t2pre</t>
-  </si>
-  <si>
-    <t>t1pre</t>
-  </si>
-  <si>
-    <t>t0</t>
-  </si>
-  <si>
-    <t>t1post</t>
-  </si>
-  <si>
-    <t>t2post</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -73,7 +53,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.64453125" customWidth="true"/>
@@ -81,108 +61,271 @@
     <col min="3" max="3" width="12.64453125" customWidth="true"/>
     <col min="4" max="4" width="12.64453125" customWidth="true"/>
     <col min="5" max="5" width="12.64453125" customWidth="true"/>
+    <col min="6" max="6" width="12.64453125" customWidth="true"/>
+    <col min="7" max="7" width="12.64453125" customWidth="true"/>
+    <col min="8" max="8" width="12.64453125" customWidth="true"/>
+    <col min="9" max="9" width="12.64453125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>4</v>
+      <c r="A1" s="0">
+        <v>60.795821130677069</v>
+      </c>
+      <c r="B1" s="0">
+        <v>0.823017793756187</v>
+      </c>
+      <c r="C1" s="0">
+        <v>0.77687888922694037</v>
+      </c>
+      <c r="D1" s="0">
+        <v>0.70570673814092455</v>
+      </c>
+      <c r="E1" s="0">
+        <v>0.61604685416674798</v>
+      </c>
+      <c r="F1" s="0">
+        <v>0.59728842918411873</v>
+      </c>
+      <c r="G1" s="0">
+        <v>0.56720305860162201</v>
+      </c>
+      <c r="H1" s="0">
+        <v>0.52420893681699343</v>
+      </c>
+      <c r="I1" s="0">
+        <v>0.4685497521358053</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0">
-        <v>52.857865220864042</v>
+        <v>0.82301779375618711</v>
       </c>
       <c r="B2" s="0">
-        <v>0.85860989096326745</v>
+        <v>54.564932016959908</v>
       </c>
       <c r="C2" s="0">
-        <v>0.65609988738115588</v>
+        <v>0.80659713312046066</v>
       </c>
       <c r="D2" s="0">
-        <v>0.60160682006776178</v>
+        <v>0.76164873315044546</v>
       </c>
       <c r="E2" s="0">
-        <v>0.55534092552017655</v>
+        <v>0.69570139645910167</v>
+      </c>
+      <c r="F2" s="0">
+        <v>0.67654354222699509</v>
+      </c>
+      <c r="G2" s="0">
+        <v>0.64479447768566034</v>
+      </c>
+      <c r="H2" s="0">
+        <v>0.59857622603922911</v>
+      </c>
+      <c r="I2" s="0">
+        <v>0.53802818717358181</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>0.85860989096326745</v>
+        <v>0.77687888922694037</v>
       </c>
       <c r="B3" s="0">
-        <v>58.455737478952159</v>
+        <v>0.80659713312046055</v>
       </c>
       <c r="C3" s="0">
-        <v>0.78783252083536892</v>
+        <v>51.537695603798873</v>
       </c>
       <c r="D3" s="0">
-        <v>0.73794821022258883</v>
+        <v>0.80092094817404202</v>
       </c>
       <c r="E3" s="0">
-        <v>0.72656870440905874</v>
+        <v>0.76258853238440294</v>
+      </c>
+      <c r="F3" s="0">
+        <v>0.74353731950202606</v>
+      </c>
+      <c r="G3" s="0">
+        <v>0.71087697713366937</v>
+      </c>
+      <c r="H3" s="0">
+        <v>0.6624608335519907</v>
+      </c>
+      <c r="I3" s="0">
+        <v>0.5983110871652163</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>0.65609988738115588</v>
+        <v>0.70570673814092455</v>
       </c>
       <c r="B4" s="0">
-        <v>0.78783252083536892</v>
+        <v>0.76164873315044535</v>
       </c>
       <c r="C4" s="0">
-        <v>47.501493838001529</v>
+        <v>0.80092094817404202</v>
       </c>
       <c r="D4" s="0">
-        <v>0.83016691347457761</v>
+        <v>51.714111891193966</v>
       </c>
       <c r="E4" s="0">
-        <v>0.74316433448323715</v>
+        <v>0.80795339503288133</v>
+      </c>
+      <c r="F4" s="0">
+        <v>0.7895948394958725</v>
+      </c>
+      <c r="G4" s="0">
+        <v>0.75699810023129899</v>
+      </c>
+      <c r="H4" s="0">
+        <v>0.70780620875335776</v>
+      </c>
+      <c r="I4" s="0">
+        <v>0.64192029542628615</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>0.60160682006776178</v>
+        <v>0.61604685416674798</v>
       </c>
       <c r="B5" s="0">
-        <v>0.73794821022258883</v>
+        <v>0.69570139645910167</v>
       </c>
       <c r="C5" s="0">
-        <v>0.83016691347457761</v>
+        <v>0.76258853238440294</v>
       </c>
       <c r="D5" s="0">
-        <v>42.257745286871959</v>
+        <v>0.80795339503288133</v>
       </c>
       <c r="E5" s="0">
-        <v>0.79749355624875717</v>
+        <v>55.094180879145206</v>
+      </c>
+      <c r="F5" s="0">
+        <v>0.8108424761823394</v>
+      </c>
+      <c r="G5" s="0">
+        <v>0.77926908236843206</v>
+      </c>
+      <c r="H5" s="0">
+        <v>0.73077840037041419</v>
+      </c>
+      <c r="I5" s="0">
+        <v>0.66515738267345492</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>0.55534092552017655</v>
+        <v>0.59728842918411884</v>
       </c>
       <c r="B6" s="0">
-        <v>0.72656870440905874</v>
+        <v>0.67654354222699509</v>
       </c>
       <c r="C6" s="0">
-        <v>0.74316433448323715</v>
+        <v>0.74353731950202606</v>
       </c>
       <c r="D6" s="0">
-        <v>0.79749355624875717</v>
+        <v>0.78959483949587261</v>
       </c>
       <c r="E6" s="0">
-        <v>40.349322709904477</v>
+        <v>0.8108424761823394</v>
+      </c>
+      <c r="F6" s="0">
+        <v>48.871572900404281</v>
+      </c>
+      <c r="G6" s="0">
+        <v>0.78839594396232227</v>
+      </c>
+      <c r="H6" s="0">
+        <v>0.75478249901706562</v>
+      </c>
+      <c r="I6" s="0">
+        <v>0.70423223424826931</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0">
+        <v>0.56720305860162201</v>
+      </c>
+      <c r="B7" s="0">
+        <v>0.64479447768566034</v>
+      </c>
+      <c r="C7" s="0">
+        <v>0.71087697713366937</v>
+      </c>
+      <c r="D7" s="0">
+        <v>0.75699810023129899</v>
+      </c>
+      <c r="E7" s="0">
+        <v>0.77926908236843206</v>
+      </c>
+      <c r="F7" s="0">
+        <v>0.78839594396232193</v>
+      </c>
+      <c r="G7" s="0">
+        <v>44.375901328422074</v>
+      </c>
+      <c r="H7" s="0">
+        <v>0.76992325829364883</v>
+      </c>
+      <c r="I7" s="0">
+        <v>0.7369427148062887</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0">
+        <v>0.52420893681699332</v>
+      </c>
+      <c r="B8" s="0">
+        <v>0.598576226039229</v>
+      </c>
+      <c r="C8" s="0">
+        <v>0.66246083355199059</v>
+      </c>
+      <c r="D8" s="0">
+        <v>0.70780620875335765</v>
+      </c>
+      <c r="E8" s="0">
+        <v>0.73077840037041419</v>
+      </c>
+      <c r="F8" s="0">
+        <v>0.75478249901706551</v>
+      </c>
+      <c r="G8" s="0">
+        <v>0.76992325829364883</v>
+      </c>
+      <c r="H8" s="0">
+        <v>41.607166163198592</v>
+      </c>
+      <c r="I8" s="0">
+        <v>0.75889726611874531</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0">
+        <v>0.46854975213580519</v>
+      </c>
+      <c r="B9" s="0">
+        <v>0.5380281871735817</v>
+      </c>
+      <c r="C9" s="0">
+        <v>0.5983110871652163</v>
+      </c>
+      <c r="D9" s="0">
+        <v>0.64192029542628626</v>
+      </c>
+      <c r="E9" s="0">
+        <v>0.66515738267345492</v>
+      </c>
+      <c r="F9" s="0">
+        <v>0.7042322342482692</v>
+      </c>
+      <c r="G9" s="0">
+        <v>0.73694271480628881</v>
+      </c>
+      <c r="H9" s="0">
+        <v>0.75889726611874531</v>
+      </c>
+      <c r="I9" s="0">
+        <v>40.565367404733848</v>
       </c>
     </row>
   </sheetData>
